--- a/docs/数据字段清单-脱敏数据申请.xlsx
+++ b/docs/数据字段清单-脱敏数据申请.xlsx
@@ -611,7 +611,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>项目组联络人：万贝　｜　指导教师：＿＿＿＿　｜　申请日期：2026 年 10 月 19 日</t>
+          <t>项目组联络人：＿＿＿＿　｜　指导教师：＿＿＿＿　｜　申请日期：2026 年 10 月 19 日</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>2025211995</t>
+          <t>2025211994</t>
         </is>
       </c>
       <c r="E2" s="6" t="inlineStr">
@@ -2473,12 +2473,12 @@
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>万贝</t>
+          <t>张三</t>
         </is>
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
-          <t>万*</t>
+          <t>张*</t>
         </is>
       </c>
       <c r="F3" s="6" t="inlineStr">
